--- a/Table S4 - PDB structures used for each virus.xlsx
+++ b/Table S4 - PDB structures used for each virus.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Obs.</t>
   </si>
   <si>
-    <t xml:space="preserve">5yxa</t>
+    <t xml:space="preserve">5YXA</t>
   </si>
   <si>
     <t xml:space="preserve">YFV</t>
@@ -66,31 +66,31 @@
     <t xml:space="preserve">C-terminal fragment only</t>
   </si>
   <si>
-    <t xml:space="preserve">8zba</t>
+    <t xml:space="preserve">8ZBA</t>
   </si>
   <si>
     <t xml:space="preserve">Tetrameric form</t>
   </si>
   <si>
-    <t xml:space="preserve">8zb9</t>
+    <t xml:space="preserve">8ZB9</t>
   </si>
   <si>
     <t xml:space="preserve">Dimeric form</t>
   </si>
   <si>
-    <t xml:space="preserve">7bsc</t>
+    <t xml:space="preserve">7BSC</t>
   </si>
   <si>
     <t xml:space="preserve">DENV2</t>
   </si>
   <si>
-    <t xml:space="preserve">7wus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7wut</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5k6k</t>
+    <t xml:space="preserve">7WUS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7WUT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5K6K</t>
   </si>
   <si>
     <t xml:space="preserve">ZIKV</t>

--- a/Table S4 - PDB structures used for each virus.xlsx
+++ b/Table S4 - PDB structures used for each virus.xlsx
@@ -81,7 +81,7 @@
     <t xml:space="preserve">7BSC</t>
   </si>
   <si>
-    <t xml:space="preserve">DENV2</t>
+    <t xml:space="preserve">DENV-2</t>
   </si>
   <si>
     <t xml:space="preserve">7WUS</t>
@@ -172,7 +172,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -191,6 +191,13 @@
       </bottom>
       <diagonal/>
     </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -217,7 +224,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -239,10 +246,26 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -507,7 +530,7 @@
   <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="19.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="25.85"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="5" style="1" width="9.14"/>
   </cols>
@@ -597,7 +620,7 @@
       <c r="B7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="7" t="n">
         <v>3.4</v>
       </c>
       <c r="D7" s="6" t="s">
@@ -611,7 +634,7 @@
       <c r="B8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="7" t="n">
         <v>3.5</v>
       </c>
       <c r="D8" s="6" t="s">
@@ -619,90 +642,90 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="12"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="8"/>
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="12"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="8"/>
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="12"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="8"/>
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="12"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="12"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="8"/>
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="12"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="8"/>
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="12"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="8"/>
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="12"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="12"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="8"/>
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="12"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="8"/>
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="12"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="8"/>
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="12"/>
     </row>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
